--- a/WorkBot/main/data/order_archive/Performance Food/Performance Food_Downtown_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/Performance Food/Performance Food_Downtown_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,69 +853,6 @@
         <v>18.98</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TN330</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Natalie's - Honey Tangerine</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="E24" t="n">
-        <v>14.57</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AH252</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Natalie's - Orange Juice</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>73.5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TN454</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Natalie's - Orange Mango</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="E26" t="n">
-        <v>13.38</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
